--- a/AAII_Financials/Yearly/SNOW_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SNOW_YR_FIN.xlsx
@@ -971,7 +971,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>60000</v>
+        <v>168600</v>
       </c>
       <c r="E14" s="3">
         <v>31400</v>
@@ -1077,7 +1077,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>6119000</v>
+        <v>6010400</v>
       </c>
       <c r="E17" s="3">
         <v>5082400</v>
@@ -1122,7 +1122,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-1435100</v>
+        <v>-1326500</v>
       </c>
       <c r="E18" s="3">
         <v>-1456000</v>
@@ -1231,7 +1231,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-1285300</v>
+        <v>-1176700</v>
       </c>
       <c r="E21" s="3">
         <v>-1333800</v>
